--- a/data/excel_database.xlsx
+++ b/data/excel_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ozzy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ozzy\OneDrive\Documents\CIVE_580_Cursor_Github\site-selector-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA52A11-D1AB-469F-958E-E58FD3934E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A8CAEC-1F06-4437-834A-DDC0BD2A116C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7254571F-48BA-4724-903E-8EE1F999C5B9}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
   <si>
     <t>https://www.ncei.noaa.gov/access/monitoring/climate-at-a-glance/statewide/time-series</t>
   </si>
@@ -358,20 +358,6 @@
     <t>Ashburn, VA</t>
   </si>
   <si>
-    <r>
-      <t>Equinix Ashburn Campus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Data Center Alley)</t>
-    </r>
-  </si>
-  <si>
     <t>Digital Realty Ashburn Campus</t>
   </si>
   <si>
@@ -379,12 +365,6 @@
   </si>
   <si>
     <t>Meta Fort Worth Data Center</t>
-  </si>
-  <si>
-    <t>Dallas, TX</t>
-  </si>
-  <si>
-    <t>Equinix Dallas (DA1)</t>
   </si>
   <si>
     <t>Santa Clara, CA</t>
@@ -765,7 +745,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -884,45 +864,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -936,62 +877,95 @@
     <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2315,15 +2289,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:colOff>1663065</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>70484</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>220163</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>34968</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>547823</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>103548</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2349,8 +2323,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6200775" y="2800349"/>
-          <a:ext cx="5563688" cy="2801029"/>
+          <a:off x="8612505" y="3987164"/>
+          <a:ext cx="5712278" cy="2898184"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2716,14 +2690,14 @@
       </c>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E2" s="40">
+      <c r="E2" s="61">
         <v>2023</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="42" t="s">
+      <c r="F2" s="62"/>
+      <c r="G2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="43"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" spans="2:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
@@ -2894,7 +2868,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.89999084444715716"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultColWidth="24.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -2903,798 +2877,766 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="C1" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="76" t="s">
+      <c r="E1" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="76" t="s">
+      <c r="G1" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="76" t="s">
+      <c r="L1" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="76" t="s">
+      <c r="M1" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="76" t="s">
+      <c r="N1" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="76" t="s">
+      <c r="O1" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="76" t="s">
+      <c r="P1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="76" t="s">
+      <c r="R1" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="76" t="s">
+      <c r="S1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="76" t="s">
+      <c r="T1" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="76" t="s">
+      <c r="U1" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="V1" s="76" t="s">
+      <c r="V1" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="W1" s="76" t="s">
+      <c r="W1" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="76" t="s">
+      <c r="X1" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="76" t="s">
+      <c r="Y1" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="Z1" s="76" t="s">
+      <c r="Z1" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="AA1" s="76" t="s">
+      <c r="AA1" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="AB1" s="76" t="s">
+      <c r="AB1" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="AC1" s="53"/>
+      <c r="AC1" s="40"/>
     </row>
     <row r="2" spans="1:29" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="57">
         <v>39.021500000000003</v>
       </c>
-      <c r="F2" s="72">
+      <c r="F2" s="57">
         <v>-77.457899999999995</v>
       </c>
-      <c r="G2" s="71">
+      <c r="G2" s="56">
         <f>(SUM(H2:S2))/12</f>
         <v>43.735000000000007</v>
       </c>
-      <c r="H2" s="71">
+      <c r="H2" s="56">
         <v>47.98</v>
       </c>
-      <c r="I2" s="73">
+      <c r="I2" s="57">
         <v>47.23</v>
       </c>
-      <c r="J2" s="73">
+      <c r="J2" s="57">
         <v>47.39</v>
       </c>
-      <c r="K2" s="73">
+      <c r="K2" s="57">
         <v>47.35</v>
       </c>
-      <c r="L2" s="73">
+      <c r="L2" s="57">
         <v>45.21</v>
       </c>
-      <c r="M2" s="73">
+      <c r="M2" s="57">
         <v>43.77</v>
       </c>
-      <c r="N2" s="73">
+      <c r="N2" s="57">
         <v>42.86</v>
       </c>
-      <c r="O2" s="73">
+      <c r="O2" s="57">
         <v>41.61</v>
       </c>
-      <c r="P2" s="73">
+      <c r="P2" s="57">
         <v>40.6</v>
       </c>
-      <c r="Q2" s="73">
+      <c r="Q2" s="57">
         <v>41.01</v>
       </c>
-      <c r="R2" s="73">
+      <c r="R2" s="57">
         <v>39.68</v>
       </c>
-      <c r="S2" s="73">
+      <c r="S2" s="57">
         <v>40.130000000000003</v>
       </c>
-      <c r="T2" s="71">
+      <c r="T2" s="56">
         <f>temperature!E4</f>
         <v>57.475000000000001</v>
       </c>
-      <c r="U2" s="73">
+      <c r="U2" s="57">
         <v>80</v>
       </c>
-      <c r="V2" s="73">
+      <c r="V2" s="57">
         <v>693</v>
       </c>
-      <c r="W2" s="73">
+      <c r="W2" s="57">
         <v>4481</v>
       </c>
-      <c r="X2" s="74">
+      <c r="X2" s="58">
         <f>water_price!K5</f>
         <v>4.9491666666666667</v>
       </c>
-      <c r="Y2" s="71">
+      <c r="Y2" s="56">
         <v>-0.63</v>
       </c>
-      <c r="Z2" s="71">
+      <c r="Z2" s="56">
         <v>-0.63</v>
       </c>
-      <c r="AA2" s="71">
+      <c r="AA2" s="56">
         <f>grid_carbon!G4</f>
         <v>235.01157662633722</v>
       </c>
-      <c r="AB2" s="75">
+      <c r="AB2" s="59">
         <f>grid_carbon!D12</f>
         <v>7767362043.1999998</v>
       </c>
-      <c r="AC2" s="53"/>
+      <c r="AC2" s="40"/>
     </row>
     <row r="3" spans="1:29" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="64">
+      <c r="E3" s="50">
         <v>32.735700000000001</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="50">
         <v>-97.434399999999997</v>
       </c>
-      <c r="G3" s="66">
+      <c r="G3" s="50">
         <v>29.31</v>
       </c>
-      <c r="H3" s="66">
+      <c r="H3" s="50">
         <v>1.38</v>
       </c>
-      <c r="I3" s="66">
+      <c r="I3" s="50">
         <v>3.97</v>
       </c>
-      <c r="J3" s="66">
+      <c r="J3" s="50">
         <v>2.76</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="50">
         <v>3.12</v>
       </c>
-      <c r="L3" s="66">
+      <c r="L3" s="50">
         <v>2.35</v>
       </c>
-      <c r="M3" s="66">
+      <c r="M3" s="50">
         <v>0.78</v>
       </c>
-      <c r="N3" s="66">
+      <c r="N3" s="50">
         <v>0.47</v>
       </c>
-      <c r="O3" s="66">
+      <c r="O3" s="50">
         <v>0.01</v>
       </c>
-      <c r="P3" s="66">
+      <c r="P3" s="50">
         <v>0.83</v>
       </c>
-      <c r="Q3" s="66">
+      <c r="Q3" s="50">
         <v>9.6300000000000008</v>
       </c>
-      <c r="R3" s="66">
+      <c r="R3" s="50">
         <v>0.47</v>
       </c>
-      <c r="S3" s="66">
+      <c r="S3" s="50">
         <v>3.55</v>
       </c>
-      <c r="T3" s="65">
+      <c r="T3" s="51">
         <f>temperature!E5</f>
         <v>68.099999999999994</v>
       </c>
-      <c r="U3" s="66">
+      <c r="U3" s="50">
         <v>98</v>
       </c>
-      <c r="V3" s="66">
+      <c r="V3" s="50">
         <v>3373</v>
       </c>
-      <c r="W3" s="66">
+      <c r="W3" s="50">
         <v>1482</v>
       </c>
-      <c r="X3" s="68">
+      <c r="X3" s="53">
         <f>water_price!K6</f>
         <v>4.2875000000000005</v>
       </c>
-      <c r="Y3" s="66">
+      <c r="Y3" s="50">
         <v>-3.87</v>
       </c>
-      <c r="Z3" s="66">
+      <c r="Z3" s="50">
         <v>-3.87</v>
       </c>
-      <c r="AA3" s="65">
+      <c r="AA3" s="51">
         <f>grid_carbon!G5</f>
         <v>338.57454215992595</v>
       </c>
-      <c r="AB3" s="69">
+      <c r="AB3" s="54">
         <f>grid_carbon!D13</f>
         <v>46684224688.5</v>
       </c>
-      <c r="AC3" s="53"/>
+      <c r="AC3" s="40"/>
     </row>
     <row r="4" spans="1:29" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="64">
+      <c r="E4" s="50">
         <v>37.3718</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="50">
         <v>-121.96939999999999</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="51">
         <f>(SUM(H4:S4))/12</f>
         <v>29.770833333333332</v>
       </c>
-      <c r="H4" s="65">
+      <c r="H4" s="51">
         <v>22.3</v>
       </c>
-      <c r="I4" s="66">
+      <c r="I4" s="50">
         <v>25.7</v>
       </c>
-      <c r="J4" s="66">
+      <c r="J4" s="50">
         <v>31.87</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="50">
         <v>31</v>
       </c>
-      <c r="L4" s="66">
+      <c r="L4" s="50">
         <v>31.72</v>
       </c>
-      <c r="M4" s="66">
+      <c r="M4" s="50">
         <v>31.68</v>
       </c>
-      <c r="N4" s="66">
+      <c r="N4" s="50">
         <v>31.68</v>
       </c>
-      <c r="O4" s="66">
+      <c r="O4" s="50">
         <v>31.7</v>
       </c>
-      <c r="P4" s="66">
+      <c r="P4" s="50">
         <v>31.46</v>
       </c>
-      <c r="Q4" s="66">
+      <c r="Q4" s="50">
         <v>31.33</v>
       </c>
-      <c r="R4" s="66">
+      <c r="R4" s="50">
         <v>31.28</v>
       </c>
-      <c r="S4" s="66">
+      <c r="S4" s="50">
         <v>25.53</v>
       </c>
-      <c r="T4" s="65">
+      <c r="T4" s="51">
         <f>temperature!E6</f>
         <v>58.250000000000007</v>
       </c>
-      <c r="U4" s="65">
+      <c r="U4" s="51">
         <v>66.5</v>
       </c>
-      <c r="V4" s="66">
+      <c r="V4" s="50">
         <v>866</v>
       </c>
-      <c r="W4" s="66">
+      <c r="W4" s="50">
         <v>3087</v>
       </c>
-      <c r="X4" s="68">
+      <c r="X4" s="53">
         <f>water_price!K7</f>
         <v>6.998333333333334</v>
       </c>
-      <c r="Y4" s="65">
+      <c r="Y4" s="51">
         <v>0.24</v>
       </c>
-      <c r="Z4" s="65">
+      <c r="Z4" s="51">
         <v>0.24</v>
       </c>
-      <c r="AA4" s="65">
+      <c r="AA4" s="51">
         <f>grid_carbon!G6</f>
         <v>160.1818447081331</v>
       </c>
-      <c r="AB4" s="69">
+      <c r="AB4" s="54">
         <f>grid_carbon!D14</f>
         <v>18478436213.5</v>
       </c>
-      <c r="AC4" s="53"/>
+      <c r="AC4" s="40"/>
     </row>
     <row r="5" spans="1:29" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="50">
         <v>33.344099999999997</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="50">
         <v>-111.6187</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="51">
         <f>(SUM(H5:S5))/12</f>
         <v>0.93416666666666659</v>
       </c>
-      <c r="H5" s="65">
+      <c r="H5" s="51">
         <v>2.21</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="50">
         <v>1.05</v>
       </c>
-      <c r="J5" s="66">
+      <c r="J5" s="50">
         <v>2.09</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="50">
         <v>0.2</v>
       </c>
-      <c r="L5" s="66">
+      <c r="L5" s="50">
         <v>0.46</v>
       </c>
-      <c r="M5" s="66">
+      <c r="M5" s="50">
         <v>0.09</v>
       </c>
-      <c r="N5" s="66">
+      <c r="N5" s="50">
         <v>0.52</v>
       </c>
-      <c r="O5" s="66">
+      <c r="O5" s="50">
         <v>1.83</v>
       </c>
-      <c r="P5" s="66">
+      <c r="P5" s="50">
         <v>1.18</v>
       </c>
-      <c r="Q5" s="66">
+      <c r="Q5" s="50">
         <v>0.19</v>
       </c>
-      <c r="R5" s="66">
+      <c r="R5" s="50">
         <v>0.47</v>
       </c>
-      <c r="S5" s="66">
+      <c r="S5" s="50">
         <v>0.92</v>
       </c>
-      <c r="T5" s="65">
+      <c r="T5" s="51">
         <f>temperature!E7</f>
         <v>60.733333333333327</v>
       </c>
-      <c r="U5" s="65">
+      <c r="U5" s="51">
         <v>95</v>
       </c>
-      <c r="V5" s="65">
+      <c r="V5" s="51">
         <v>3175</v>
       </c>
-      <c r="W5" s="65">
+      <c r="W5" s="51">
         <v>2062</v>
       </c>
-      <c r="X5" s="68">
+      <c r="X5" s="53">
         <f>water_price!K8</f>
         <v>3.3783333333333334</v>
       </c>
-      <c r="Y5" s="65">
+      <c r="Y5" s="51">
         <v>1.31</v>
       </c>
-      <c r="Z5" s="65">
+      <c r="Z5" s="51">
         <v>1.31</v>
       </c>
-      <c r="AA5" s="65">
+      <c r="AA5" s="51">
         <f>grid_carbon!G7</f>
         <v>308.47988124615426</v>
       </c>
-      <c r="AB5" s="69">
+      <c r="AB5" s="54">
         <f>grid_carbon!D15</f>
         <v>9539844180.7999992</v>
       </c>
-      <c r="AC5" s="53"/>
+      <c r="AC5" s="40"/>
     </row>
     <row r="6" spans="1:29" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="50">
         <v>41.8536</v>
       </c>
-      <c r="F6" s="64">
+      <c r="F6" s="50">
         <v>-87.618200000000002</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="51">
         <f>(SUM(H6:S6))/12</f>
         <v>2.8874999999999997</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H6" s="51">
         <v>2.62</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="50">
         <v>2.83</v>
       </c>
-      <c r="J6" s="66">
+      <c r="J6" s="50">
         <v>4.34</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="50">
         <v>2.5499999999999998</v>
       </c>
-      <c r="L6" s="66">
+      <c r="L6" s="50">
         <v>2.48</v>
       </c>
-      <c r="M6" s="66">
+      <c r="M6" s="50">
         <v>1.89</v>
       </c>
-      <c r="N6" s="66">
+      <c r="N6" s="50">
         <v>4.75</v>
       </c>
-      <c r="O6" s="66">
+      <c r="O6" s="50">
         <v>4.01</v>
       </c>
-      <c r="P6" s="66">
+      <c r="P6" s="50">
         <v>2.4</v>
       </c>
-      <c r="Q6" s="66">
+      <c r="Q6" s="50">
         <v>3.3</v>
       </c>
-      <c r="R6" s="66">
+      <c r="R6" s="50">
         <v>0.72</v>
       </c>
-      <c r="S6" s="66">
+      <c r="S6" s="50">
         <v>2.76</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="51">
         <f>temperature!E8</f>
         <v>54.741666666666667</v>
       </c>
-      <c r="U6" s="66">
+      <c r="U6" s="50">
         <v>82</v>
       </c>
-      <c r="V6" s="66">
+      <c r="V6" s="50">
         <v>881</v>
       </c>
-      <c r="W6" s="66">
+      <c r="W6" s="50">
         <v>5320</v>
       </c>
-      <c r="X6" s="68">
+      <c r="X6" s="53">
         <f>water_price!K9</f>
         <v>3.8800000000000003</v>
       </c>
-      <c r="Y6" s="66">
+      <c r="Y6" s="50">
         <v>-0.99250000000000005</v>
       </c>
-      <c r="Z6" s="66">
+      <c r="Z6" s="50">
         <v>-0.99250000000000005</v>
       </c>
-      <c r="AA6" s="65">
+      <c r="AA6" s="51">
         <f>grid_carbon!G8</f>
         <v>212.67301505368803</v>
       </c>
-      <c r="AB6" s="69">
+      <c r="AB6" s="54">
         <f>grid_carbon!D16</f>
         <v>15161020777.299999</v>
       </c>
-      <c r="AC6" s="53"/>
+      <c r="AC6" s="40"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="AC7" s="53"/>
+      <c r="AC7" s="40"/>
     </row>
     <row r="8" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AC8" s="53"/>
+      <c r="AC8" s="40"/>
     </row>
     <row r="9" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="61" t="s">
+      <c r="E9" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="AC9" s="53"/>
-    </row>
-    <row r="10" spans="1:29" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="61" t="s">
+      <c r="AC9" s="40"/>
+    </row>
+    <row r="10" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="62">
-        <v>39.016300000000001</v>
-      </c>
-      <c r="E10" s="62">
-        <v>-77.459000000000003</v>
-      </c>
-      <c r="AC10" s="53"/>
+      <c r="D10" s="48">
+        <v>39.021500000000003</v>
+      </c>
+      <c r="E10" s="48">
+        <v>-77.457899999999995</v>
+      </c>
+      <c r="AC10" s="40"/>
     </row>
     <row r="11" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="62"/>
-      <c r="B11" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="63" t="s">
+      <c r="A11" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="62">
-        <v>39.021500000000003</v>
-      </c>
-      <c r="E11" s="62">
-        <v>-77.457899999999995</v>
-      </c>
-      <c r="AC11" s="53"/>
+      <c r="C11" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="48">
+        <v>32.735700000000001</v>
+      </c>
+      <c r="E11" s="48">
+        <v>-97.434399999999997</v>
+      </c>
+      <c r="AC11" s="40"/>
     </row>
     <row r="12" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="63" t="s">
+      <c r="A12" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="62">
-        <v>32.735700000000001</v>
-      </c>
-      <c r="E12" s="62">
-        <v>-97.434399999999997</v>
-      </c>
-      <c r="AC12" s="53"/>
-    </row>
-    <row r="13" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="62"/>
-      <c r="B13" s="62" t="s">
+      <c r="C12" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="D12" s="48">
+        <v>37.3718</v>
+      </c>
+      <c r="E12" s="48">
+        <v>-121.96939999999999</v>
+      </c>
+      <c r="AC12" s="40"/>
+    </row>
+    <row r="13" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="62">
-        <v>32.800899999999999</v>
-      </c>
-      <c r="E13" s="62">
-        <v>-96.819500000000005</v>
-      </c>
-      <c r="AC13" s="53"/>
+      <c r="C13" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="48">
+        <v>33.344099999999997</v>
+      </c>
+      <c r="E13" s="48">
+        <v>-111.6187</v>
+      </c>
+      <c r="AC13" s="40"/>
     </row>
     <row r="14" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="63" t="s">
+      <c r="A14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="62">
-        <v>37.3718</v>
-      </c>
-      <c r="E14" s="62">
-        <v>-121.96939999999999</v>
-      </c>
-      <c r="AC14" s="53"/>
-    </row>
-    <row r="15" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="62" t="s">
+      <c r="C14" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="62">
-        <v>33.344099999999997</v>
-      </c>
-      <c r="E15" s="62">
-        <v>-111.6187</v>
-      </c>
-      <c r="AC15" s="53"/>
-    </row>
-    <row r="16" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="62">
+      <c r="D14" s="48">
         <v>41.8536</v>
       </c>
-      <c r="E16" s="62">
+      <c r="E14" s="48">
         <v>-87.618200000000002</v>
       </c>
-      <c r="AC16" s="53"/>
+      <c r="AC14" s="40"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC15" s="40"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AC16" s="40"/>
     </row>
     <row r="17" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC17" s="53"/>
+      <c r="AC17" s="40"/>
     </row>
     <row r="18" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC18" s="53"/>
+      <c r="AC18" s="40"/>
     </row>
     <row r="19" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC19" s="53"/>
+      <c r="AC19" s="40"/>
     </row>
     <row r="20" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC20" s="53"/>
+      <c r="AC20" s="40"/>
     </row>
     <row r="21" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC21" s="53"/>
+      <c r="AC21" s="40"/>
     </row>
     <row r="22" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC22" s="53"/>
+      <c r="AC22" s="40"/>
     </row>
     <row r="23" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC23" s="53"/>
+      <c r="AC23" s="40"/>
     </row>
     <row r="24" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC24" s="53"/>
+      <c r="AC24" s="40"/>
     </row>
     <row r="25" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC25" s="53"/>
+      <c r="AC25" s="40"/>
     </row>
     <row r="26" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC26" s="53"/>
+      <c r="AC26" s="40"/>
     </row>
     <row r="27" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC27" s="53"/>
+      <c r="AC27" s="40"/>
     </row>
     <row r="28" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC28" s="53"/>
+      <c r="AC28" s="40"/>
     </row>
     <row r="29" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC29" s="53"/>
+      <c r="AC29" s="40"/>
     </row>
     <row r="30" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC30" s="53"/>
+      <c r="AC30" s="40"/>
     </row>
     <row r="31" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC31" s="53"/>
+      <c r="AC31" s="40"/>
     </row>
     <row r="32" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC32" s="53"/>
+      <c r="AC32" s="40"/>
     </row>
     <row r="33" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC33" s="53"/>
+      <c r="AC33" s="40"/>
     </row>
     <row r="34" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC34" s="53"/>
+      <c r="AC34" s="40"/>
     </row>
     <row r="35" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC35" s="53"/>
+      <c r="AC35" s="40"/>
     </row>
     <row r="36" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC36" s="53"/>
+      <c r="AC36" s="40"/>
     </row>
     <row r="37" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC37" s="53"/>
+      <c r="AC37" s="40"/>
     </row>
     <row r="38" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC38" s="53"/>
+      <c r="AC38" s="40"/>
     </row>
     <row r="39" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC39" s="53"/>
+      <c r="AC39" s="40"/>
     </row>
     <row r="40" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC40" s="53"/>
+      <c r="AC40" s="40"/>
     </row>
     <row r="41" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC41" s="53"/>
+      <c r="AC41" s="40"/>
     </row>
     <row r="42" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC42" s="53"/>
+      <c r="AC42" s="40"/>
     </row>
     <row r="43" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC43" s="53"/>
+      <c r="AC43" s="40"/>
     </row>
     <row r="44" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC44" s="53"/>
+      <c r="AC44" s="40"/>
     </row>
     <row r="45" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC45" s="53"/>
+      <c r="AC45" s="40"/>
     </row>
     <row r="46" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC46" s="53"/>
+      <c r="AC46" s="40"/>
     </row>
     <row r="47" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC47" s="53"/>
+      <c r="AC47" s="40"/>
     </row>
     <row r="48" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC48" s="53"/>
-    </row>
-    <row r="49" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC49" s="53"/>
-    </row>
-    <row r="50" spans="29:29" x14ac:dyDescent="0.3">
-      <c r="AC50" s="53"/>
+      <c r="AC48" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3735,21 +3677,21 @@
       <c r="S2" s="5"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="47" t="s">
+      <c r="G3" s="66"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50" t="s">
+      <c r="J3" s="69"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="73"/>
       <c r="S3" s="5"/>
     </row>
     <row r="4" spans="2:20" ht="52.8" x14ac:dyDescent="0.3">
@@ -4234,10 +4176,10 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="46">
         <f>E10*10</f>
         <v>85.3</v>
       </c>
@@ -4246,11 +4188,11 @@
       <c r="B10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="57">
+      <c r="D10" s="74"/>
+      <c r="E10" s="44">
         <v>8.5299999999999994</v>
       </c>
     </row>
@@ -4269,10 +4211,10 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="41">
         <v>91059344</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="42">
         <f>C12*($E$9)</f>
         <v>7767362043.1999998</v>
       </c>
@@ -4284,10 +4226,10 @@
       <c r="B13" s="1">
         <v>2</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="41">
         <v>547294545</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="42">
         <f t="shared" ref="D13:D16" si="1">C13*($E$9)</f>
         <v>46684224688.5</v>
       </c>
@@ -4299,10 +4241,10 @@
       <c r="B14" s="1">
         <v>3</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="41">
         <v>216628795</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="42">
         <f t="shared" si="1"/>
         <v>18478436213.5</v>
       </c>
@@ -4314,10 +4256,10 @@
       <c r="B15" s="1">
         <v>4</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="41">
         <v>111838736</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="42">
         <f t="shared" si="1"/>
         <v>9539844180.7999992</v>
       </c>
@@ -4329,16 +4271,16 @@
       <c r="B16" s="1">
         <v>5</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="41">
         <v>177737641</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="42">
         <f t="shared" si="1"/>
         <v>15161020777.299999</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="45" t="s">
         <v>81</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -4346,7 +4288,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="45" t="s">
         <v>84</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -4354,12 +4296,12 @@
       </c>
     </row>
     <row r="21" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="45" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="45" t="s">
         <v>86</v>
       </c>
     </row>
